--- a/source-excel/Driver.xlsx
+++ b/source-excel/Driver.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI\รายงานการจัดระดับ\newstarrating\source-excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{764043D8-2AC5-461A-95B2-FD00C4327598}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06BB778D-05D7-4CAE-9D32-51D04F80C66D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="8130" xr2:uid="{5FA2FF11-DEAD-479A-BBC7-1C4C4477CC4E}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18525" uniqueCount="6397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18510" uniqueCount="6397">
   <si>
     <t>ลำดับ</t>
   </si>
@@ -20055,7 +20055,7 @@
         <v>5579</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>3599</v>
+        <v>3583</v>
       </c>
       <c r="J10" s="12" t="s">
         <v>2376</v>
@@ -20063,8 +20063,8 @@
       <c r="K10" s="12" t="s">
         <v>5580</v>
       </c>
-      <c r="L10" s="13" t="s">
-        <v>3599</v>
+      <c r="L10" s="13">
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -20511,7 +20511,7 @@
         <v>5579</v>
       </c>
       <c r="I22" s="12" t="s">
-        <v>3599</v>
+        <v>3583</v>
       </c>
       <c r="J22" s="12" t="s">
         <v>2376</v>
@@ -20519,8 +20519,8 @@
       <c r="K22" s="12" t="s">
         <v>5625</v>
       </c>
-      <c r="L22" s="13" t="s">
-        <v>3599</v>
+      <c r="L22" s="13">
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -20739,7 +20739,7 @@
         <v>5579</v>
       </c>
       <c r="I28" s="12" t="s">
-        <v>3599</v>
+        <v>3583</v>
       </c>
       <c r="J28" s="12" t="s">
         <v>2376</v>
@@ -20747,8 +20747,8 @@
       <c r="K28" s="12" t="s">
         <v>5644</v>
       </c>
-      <c r="L28" s="13" t="s">
-        <v>3599</v>
+      <c r="L28" s="13">
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -27465,7 +27465,7 @@
         <v>5995</v>
       </c>
       <c r="I205" s="12" t="s">
-        <v>3599</v>
+        <v>3583</v>
       </c>
       <c r="J205" s="12" t="s">
         <v>3613</v>
@@ -27473,8 +27473,8 @@
       <c r="K205" s="12" t="s">
         <v>5443</v>
       </c>
-      <c r="L205" s="13" t="s">
-        <v>3599</v>
+      <c r="L205" s="13">
+        <v>9</v>
       </c>
     </row>
     <row r="206" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -27503,7 +27503,7 @@
         <v>5995</v>
       </c>
       <c r="I206" s="12" t="s">
-        <v>3599</v>
+        <v>3583</v>
       </c>
       <c r="J206" s="12" t="s">
         <v>3613</v>
@@ -27511,8 +27511,8 @@
       <c r="K206" s="12" t="s">
         <v>4200</v>
       </c>
-      <c r="L206" s="13" t="s">
-        <v>3599</v>
+      <c r="L206" s="13">
+        <v>9</v>
       </c>
     </row>
     <row r="207" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -27541,7 +27541,7 @@
         <v>5995</v>
       </c>
       <c r="I207" s="12" t="s">
-        <v>3599</v>
+        <v>3583</v>
       </c>
       <c r="J207" s="12" t="s">
         <v>3613</v>
@@ -27549,8 +27549,8 @@
       <c r="K207" s="12" t="s">
         <v>4201</v>
       </c>
-      <c r="L207" s="13" t="s">
-        <v>3599</v>
+      <c r="L207" s="13">
+        <v>9</v>
       </c>
     </row>
     <row r="208" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -27579,7 +27579,7 @@
         <v>5995</v>
       </c>
       <c r="I208" s="12" t="s">
-        <v>3599</v>
+        <v>3583</v>
       </c>
       <c r="J208" s="12" t="s">
         <v>3613</v>
@@ -27587,8 +27587,8 @@
       <c r="K208" s="12" t="s">
         <v>4202</v>
       </c>
-      <c r="L208" s="13" t="s">
-        <v>3599</v>
+      <c r="L208" s="13">
+        <v>9</v>
       </c>
     </row>
     <row r="209" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -27617,7 +27617,7 @@
         <v>5995</v>
       </c>
       <c r="I209" s="12" t="s">
-        <v>3599</v>
+        <v>3583</v>
       </c>
       <c r="J209" s="12" t="s">
         <v>3613</v>
@@ -27625,8 +27625,8 @@
       <c r="K209" s="12" t="s">
         <v>5445</v>
       </c>
-      <c r="L209" s="13" t="s">
-        <v>3599</v>
+      <c r="L209" s="13">
+        <v>9</v>
       </c>
     </row>
     <row r="210" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -27655,7 +27655,7 @@
         <v>5995</v>
       </c>
       <c r="I210" s="12" t="s">
-        <v>3599</v>
+        <v>3583</v>
       </c>
       <c r="J210" s="12" t="s">
         <v>3613</v>
@@ -27663,8 +27663,8 @@
       <c r="K210" s="12" t="s">
         <v>4203</v>
       </c>
-      <c r="L210" s="13" t="s">
-        <v>3599</v>
+      <c r="L210" s="13">
+        <v>9</v>
       </c>
     </row>
     <row r="211" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -60753,7 +60753,7 @@
         <v>5310</v>
       </c>
       <c r="I1081" s="12" t="s">
-        <v>3599</v>
+        <v>3583</v>
       </c>
       <c r="J1081" s="12" t="s">
         <v>3615</v>
@@ -60761,8 +60761,8 @@
       <c r="K1081" s="12" t="s">
         <v>4856</v>
       </c>
-      <c r="L1081" s="13" t="s">
-        <v>3599</v>
+      <c r="L1081" s="13">
+        <v>9</v>
       </c>
     </row>
     <row r="1082" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -60791,7 +60791,7 @@
         <v>5310</v>
       </c>
       <c r="I1082" s="12" t="s">
-        <v>3599</v>
+        <v>3583</v>
       </c>
       <c r="J1082" s="12" t="s">
         <v>3615</v>
@@ -60799,8 +60799,8 @@
       <c r="K1082" s="12" t="s">
         <v>4857</v>
       </c>
-      <c r="L1082" s="13" t="s">
-        <v>3599</v>
+      <c r="L1082" s="13">
+        <v>9</v>
       </c>
     </row>
     <row r="1083" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -60829,7 +60829,7 @@
         <v>5310</v>
       </c>
       <c r="I1083" s="12" t="s">
-        <v>3599</v>
+        <v>3583</v>
       </c>
       <c r="J1083" s="12" t="s">
         <v>3615</v>
@@ -60837,8 +60837,8 @@
       <c r="K1083" s="12" t="s">
         <v>4858</v>
       </c>
-      <c r="L1083" s="13" t="s">
-        <v>3599</v>
+      <c r="L1083" s="13">
+        <v>9</v>
       </c>
     </row>
     <row r="1084" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -60867,7 +60867,7 @@
         <v>5310</v>
       </c>
       <c r="I1084" s="12" t="s">
-        <v>3599</v>
+        <v>3583</v>
       </c>
       <c r="J1084" s="12" t="s">
         <v>3615</v>
@@ -60875,8 +60875,8 @@
       <c r="K1084" s="12" t="s">
         <v>4859</v>
       </c>
-      <c r="L1084" s="13" t="s">
-        <v>3599</v>
+      <c r="L1084" s="13">
+        <v>9</v>
       </c>
     </row>
     <row r="1085" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -67707,7 +67707,7 @@
         <v>6178</v>
       </c>
       <c r="I1264" s="12" t="s">
-        <v>3599</v>
+        <v>3583</v>
       </c>
       <c r="J1264" s="12" t="s">
         <v>3615</v>
@@ -67715,8 +67715,8 @@
       <c r="K1264" s="12" t="s">
         <v>4855</v>
       </c>
-      <c r="L1264" s="13" t="s">
-        <v>3599</v>
+      <c r="L1264" s="13">
+        <v>9</v>
       </c>
     </row>
     <row r="1265" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -77055,7 +77055,7 @@
         <v>6253</v>
       </c>
       <c r="I1510" s="12" t="s">
-        <v>3599</v>
+        <v>3583</v>
       </c>
       <c r="J1510" s="12" t="s">
         <v>1626</v>
@@ -77063,8 +77063,8 @@
       <c r="K1510" s="12" t="s">
         <v>6347</v>
       </c>
-      <c r="L1510" s="13" t="s">
-        <v>3599</v>
+      <c r="L1510" s="13">
+        <v>9</v>
       </c>
     </row>
     <row r="1511" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -85884,11 +85884,11 @@
       </c>
       <c r="E175" s="10">
         <f>COUNTIFS(รายชื่อจบส.!$A:$A,$B175,รายชื่อจบส.!$I:$I,"ผ่าน")</f>
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F175" s="10">
         <f t="shared" si="4"/>
-        <v>-10</v>
+        <v>-7</v>
       </c>
       <c r="G175" s="10">
         <f t="shared" si="5"/>
@@ -85896,7 +85896,7 @@
       </c>
       <c r="H175" s="10">
         <f>_xlfn.MAXIFS(รายชื่อจบส.!$L:$L,รายชื่อจบส.!$A:$A,$B175)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="176" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.65">
@@ -86008,11 +86008,11 @@
       </c>
       <c r="E179" s="10">
         <f>COUNTIFS(รายชื่อจบส.!$A:$A,$B179,รายชื่อจบส.!$I:$I,"ผ่าน")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F179" s="10">
         <f t="shared" si="4"/>
-        <v>-27</v>
+        <v>-26</v>
       </c>
       <c r="G179" s="10">
         <f t="shared" si="5"/>
@@ -86020,7 +86020,7 @@
       </c>
       <c r="H179" s="10">
         <f>_xlfn.MAXIFS(รายชื่อจบส.!$L:$L,รายชื่อจบส.!$A:$A,$B179)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="180" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.65">
@@ -87589,19 +87589,19 @@
       </c>
       <c r="E230" s="10">
         <f>COUNTIFS(รายชื่อจบส.!$A:$A,$B230,รายชื่อจบส.!$I:$I,"ผ่าน")</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F230" s="10">
         <f t="shared" si="6"/>
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="G230" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H230" s="10">
         <f>_xlfn.MAXIFS(รายชื่อจบส.!$L:$L,รายชื่อจบส.!$A:$A,$B230)</f>
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="231" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.65">
@@ -87682,11 +87682,11 @@
       </c>
       <c r="E233" s="10">
         <f>COUNTIFS(รายชื่อจบส.!$A:$A,$B233,รายชื่อจบส.!$I:$I,"ผ่าน")</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F233" s="10">
         <f t="shared" si="6"/>
-        <v>-6</v>
+        <v>-2</v>
       </c>
       <c r="G233" s="10">
         <f t="shared" si="7"/>
@@ -87694,7 +87694,7 @@
       </c>
       <c r="H233" s="10">
         <f>_xlfn.MAXIFS(รายชื่อจบส.!$L:$L,รายชื่อจบส.!$A:$A,$B233)</f>
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="234" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.65">
@@ -87713,19 +87713,19 @@
       </c>
       <c r="E234" s="10">
         <f>COUNTIFS(รายชื่อจบส.!$A:$A,$B234,รายชื่อจบส.!$I:$I,"ผ่าน")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F234" s="10">
         <f t="shared" si="6"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G234" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H234" s="10">
         <f>_xlfn.MAXIFS(รายชื่อจบส.!$L:$L,รายชื่อจบส.!$A:$A,$B234)</f>
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="235" spans="1:8" ht="17.5" thickBot="1" x14ac:dyDescent="0.65">

--- a/source-excel/Driver.xlsx
+++ b/source-excel/Driver.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI\รายงานการจัดระดับ\newstarrating\source-excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{837BC9A1-342C-4AE4-8EA0-4773A5C5318D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65F31432-32A0-4D31-BBD0-D8C59A2E81A7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="8130" activeTab="1" xr2:uid="{5FA2FF11-DEAD-479A-BBC7-1C4C4477CC4E}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="8130" xr2:uid="{5FA2FF11-DEAD-479A-BBC7-1C4C4477CC4E}"/>
   </bookViews>
   <sheets>
     <sheet name="รายชื่อจบส." sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'จบส.-Score'!$B$1:$H$288</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">รายชื่อจบส.!$A$1:$L$1480</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">รายชื่อจบส.!$A$1:$L$1482</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -56081,7 +56081,7 @@
         <v>4316</v>
       </c>
       <c r="I969" s="12" t="s">
-        <v>3060</v>
+        <v>3059</v>
       </c>
       <c r="J969" s="12" t="s">
         <v>1603</v>
@@ -56090,7 +56090,7 @@
         <v>3912</v>
       </c>
       <c r="L969" s="13">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="970" spans="1:12" x14ac:dyDescent="0.55000000000000004">
@@ -56157,7 +56157,7 @@
         <v>4316</v>
       </c>
       <c r="I971" s="12" t="s">
-        <v>3060</v>
+        <v>3059</v>
       </c>
       <c r="J971" s="12" t="s">
         <v>1603</v>
@@ -65201,7 +65201,7 @@
         <v>4319</v>
       </c>
       <c r="I1209" s="12" t="s">
-        <v>3060</v>
+        <v>3059</v>
       </c>
       <c r="J1209" s="12" t="s">
         <v>1603</v>
@@ -75588,7 +75588,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L1480" xr:uid="{21331360-3A0F-429C-BBD5-B83B70A5E183}"/>
+  <autoFilter ref="A1:L1482" xr:uid="{21331360-3A0F-429C-BBD5-B83B70A5E183}"/>
   <sortState ref="A2:L1280">
     <sortCondition ref="A2:A1280"/>
   </sortState>
@@ -76153,15 +76153,15 @@
       </c>
       <c r="E18" s="10">
         <f>COUNTIFS(รายชื่อจบส.!$A:$A,$B18,รายชื่อจบส.!$I:$I,"ผ่าน")</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F18" s="10">
         <f t="shared" si="0"/>
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="G18" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H18" s="10">
         <f>_xlfn.MAXIFS(รายชื่อจบส.!$L:$L,รายชื่อจบส.!$A:$A,$B18)</f>
@@ -76246,15 +76246,15 @@
       </c>
       <c r="E21" s="10">
         <f>COUNTIFS(รายชื่อจบส.!$A:$A,$B21,รายชื่อจบส.!$I:$I,"ผ่าน")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F21" s="10">
         <f t="shared" si="0"/>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G21" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H21" s="10">
         <f>_xlfn.MAXIFS(รายชื่อจบส.!$L:$L,รายชื่อจบส.!$A:$A,$B21)</f>
